--- a/PAMF_DIG F2 - monthly2026-07-29.xlsx
+++ b/PAMF_DIG F2 - monthly2026-07-29.xlsx
@@ -9320,7 +9320,7 @@
         <v>0.09</v>
       </c>
       <c r="N122" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
@@ -11948,7 +11948,7 @@
         <v>0.09</v>
       </c>
       <c r="N158" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
@@ -19175,7 +19175,7 @@
         <v>0.09</v>
       </c>
       <c r="N257" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O257" t="inlineStr">
         <is>
@@ -20124,7 +20124,7 @@
         <v>0.09</v>
       </c>
       <c r="N270" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O270" t="inlineStr">
         <is>
@@ -21219,7 +21219,7 @@
         <v>0.09</v>
       </c>
       <c r="N285" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O285" t="inlineStr">
         <is>
@@ -21584,7 +21584,7 @@
         <v>0.09</v>
       </c>
       <c r="N290" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O290" t="inlineStr">
         <is>
@@ -23774,7 +23774,7 @@
         <v>0.09</v>
       </c>
       <c r="N320" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O320" t="inlineStr">
         <is>

--- a/PAMF_DIG F2 - monthly2026-07-29.xlsx
+++ b/PAMF_DIG F2 - monthly2026-07-29.xlsx
@@ -2093,7 +2093,7 @@
         <v>0.09</v>
       </c>
       <c r="N23" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>0.09</v>
       </c>
       <c r="N30" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>0.09</v>
       </c>
       <c r="N59" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>0.09</v>
       </c>
       <c r="N109" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
@@ -12094,7 +12094,7 @@
         <v>0.09</v>
       </c>
       <c r="N160" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O160" t="inlineStr">
         <is>
@@ -19321,7 +19321,7 @@
         <v>0.09</v>
       </c>
       <c r="N259" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O259" t="inlineStr">
         <is>
@@ -20270,7 +20270,7 @@
         <v>0.09</v>
       </c>
       <c r="N272" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O272" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>0.09</v>
       </c>
       <c r="N295" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O295" t="inlineStr">
         <is>
@@ -22241,7 +22241,7 @@
         <v>0.09</v>
       </c>
       <c r="N299" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O299" t="inlineStr">
         <is>
@@ -23482,7 +23482,7 @@
         <v>0.09</v>
       </c>
       <c r="N316" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O316" t="inlineStr">
         <is>
@@ -25745,7 +25745,7 @@
         <v>0.09</v>
       </c>
       <c r="N347" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O347" t="inlineStr">
         <is>
@@ -26548,7 +26548,7 @@
         <v>0.09</v>
       </c>
       <c r="N358" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O358" t="inlineStr">
         <is>
@@ -28081,7 +28081,7 @@
         <v>0.09</v>
       </c>
       <c r="N379" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O379" t="inlineStr">
         <is>
@@ -31074,7 +31074,7 @@
         <v>0.09</v>
       </c>
       <c r="N420" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O420" t="inlineStr">
         <is>
